--- a/paper_aaai2027/COC_REPORT/ablations_results/DISTIL_ablation_results.xlsx
+++ b/paper_aaai2027/COC_REPORT/ablations_results/DISTIL_ablation_results.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D4_FailureCount" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D5_Compute" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1_SignTest" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D5_vs_DiffDAgger" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -44,7 +45,7 @@
     <numFmt numFmtId="166" formatCode="0.0\×"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -193,6 +194,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -270,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -485,6 +489,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10219,6 +10227,778 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="76" min="1" max="1"/>
+    <col width="10" customWidth="1" style="76" min="2" max="2"/>
+    <col width="15" customWidth="1" style="76" min="3" max="3"/>
+    <col width="15" customWidth="1" style="76" min="4" max="4"/>
+    <col width="15" customWidth="1" style="76" min="5" max="5"/>
+    <col width="15" customWidth="1" style="76" min="6" max="6"/>
+    <col width="15" customWidth="1" style="76" min="7" max="7"/>
+    <col width="15" customWidth="1" style="76" min="8" max="8"/>
+    <col width="15" customWidth="1" style="76" min="9" max="9"/>
+    <col width="15" customWidth="1" style="76" min="10" max="10"/>
+    <col width="15" customWidth="1" style="76" min="11" max="11"/>
+    <col width="15" customWidth="1" style="76" min="12" max="12"/>
+    <col width="15" customWidth="1" style="76" min="13" max="13"/>
+    <col width="15" customWidth="1" style="76" min="14" max="14"/>
+    <col width="15" customWidth="1" style="76" min="15" max="15"/>
+    <col width="15" customWidth="1" style="76" min="16" max="16"/>
+    <col width="15" customWidth="1" style="76" min="17" max="17"/>
+    <col width="15" customWidth="1" style="76" min="18" max="18"/>
+    <col width="15" customWidth="1" style="76" min="19" max="19"/>
+    <col width="15" customWidth="1" style="76" min="20" max="20"/>
+    <col width="15" customWidth="1" style="76" min="21" max="21"/>
+    <col width="15" customWidth="1" style="76" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>D5 — Per-round compute: DISEIL vs Diff-DAgger baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="88" t="inlineStr">
+        <is>
+          <t>Companion to D5_Compute (which uses SafeDAgger). This sheet does NOT modify that one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Method arm 'full' = DISEIL. Baseline arm = 'diffdagger' (distil/config.py:160 BASELINE_ARMS -&gt; distil/diffdagger.py::run_diffdagger).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Seed 1 only. Backend: OpenRouter (VLM qwen/qwen3-vl-30b-a3b-instruct, LLM qwen/qwen3-32b). Diff-DAgger uses NO foundation model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P1 = the run's FIRST round (round 0). P5 = mean ± sample SD (ddof=1) over rounds 0..4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Diff-DAgger token columns are 0 BY CONSTRUCTION (no VLM/LLM/KAG in the arm) — not missing data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="inlineStr">
+        <is>
+          <t>n rounds (DISEIL)</t>
+        </is>
+      </c>
+      <c r="D8" s="89" t="inlineStr">
+        <is>
+          <t>n rounds (Diff-DAgger)</t>
+        </is>
+      </c>
+      <c r="E8" s="89" t="inlineStr">
+        <is>
+          <t>Diff-DAgger s/round</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>DISEIL s/round</t>
+        </is>
+      </c>
+      <c r="G8" s="89" t="inlineStr">
+        <is>
+          <t>Overhead x</t>
+        </is>
+      </c>
+      <c r="H8" s="89" t="inlineStr">
+        <is>
+          <t>Shared train+eval s (DISEIL)</t>
+        </is>
+      </c>
+      <c r="I8" s="89" t="inlineStr">
+        <is>
+          <t>Shared train+eval s (Diff-DAgger)</t>
+        </is>
+      </c>
+      <c r="J8" s="89" t="inlineStr">
+        <is>
+          <t>DISEIL screening s</t>
+        </is>
+      </c>
+      <c r="K8" s="89" t="inlineStr">
+        <is>
+          <t>DISEIL analysis+prescription s</t>
+        </is>
+      </c>
+      <c r="L8" s="89" t="inlineStr">
+        <is>
+          <t>DISEIL-specific s</t>
+        </is>
+      </c>
+      <c r="M8" s="89" t="inlineStr">
+        <is>
+          <t>Diff-DAgger gate s</t>
+        </is>
+      </c>
+      <c r="N8" s="89" t="inlineStr">
+        <is>
+          <t>Reasoning-only add-on s</t>
+        </is>
+      </c>
+      <c r="O8" s="89" t="inlineStr">
+        <is>
+          <t>VLM tok/round</t>
+        </is>
+      </c>
+      <c r="P8" s="89" t="inlineStr">
+        <is>
+          <t>LLM tok/round</t>
+        </is>
+      </c>
+      <c r="Q8" s="89" t="inlineStr">
+        <is>
+          <t>Reasoning-LLM tok/round</t>
+        </is>
+      </c>
+      <c r="R8" s="89" t="inlineStr">
+        <is>
+          <t>KAG tok contribution</t>
+        </is>
+      </c>
+      <c r="S8" s="89" t="inlineStr">
+        <is>
+          <t>Diff-DAgger VLM tok</t>
+        </is>
+      </c>
+      <c r="T8" s="89" t="inlineStr">
+        <is>
+          <t>Diff-DAgger LLM tok</t>
+        </is>
+      </c>
+      <c r="U8" s="89" t="inlineStr">
+        <is>
+          <t>Diff-DAgger reasoning tok</t>
+        </is>
+      </c>
+      <c r="V8" s="89" t="inlineStr">
+        <is>
+          <t>Diff-DAgger KAG tok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="87" t="inlineStr">
+        <is>
+          <t>— PROTOCOL P1 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Door/state</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>734</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1054.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="H10" t="n">
+        <v>783</v>
+      </c>
+      <c r="I10" t="n">
+        <v>721</v>
+      </c>
+      <c r="J10" t="n">
+        <v>205</v>
+      </c>
+      <c r="K10" t="n">
+        <v>66</v>
+      </c>
+      <c r="L10" t="n">
+        <v>271</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>258</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3258</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8253</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3486</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3195</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Door/image</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1180</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1052</v>
+      </c>
+      <c r="J11" t="n">
+        <v>201</v>
+      </c>
+      <c r="K11" t="n">
+        <v>93</v>
+      </c>
+      <c r="L11" t="n">
+        <v>294</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13</v>
+      </c>
+      <c r="N11" t="n">
+        <v>281</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3293</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8086</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3004</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3195</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wipe/image</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1652</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2194.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1491</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1475</v>
+      </c>
+      <c r="J12" t="n">
+        <v>431</v>
+      </c>
+      <c r="K12" t="n">
+        <v>273</v>
+      </c>
+      <c r="L12" t="n">
+        <v>704</v>
+      </c>
+      <c r="M12" t="n">
+        <v>177</v>
+      </c>
+      <c r="N12" t="n">
+        <v>527</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3228</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6332</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2303</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2392</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="87" t="inlineStr">
+        <is>
+          <t>— PROTOCOL P5 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Door/state</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>668.8 ± 58.5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>783.0 ± 183.7</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>547.8 ± 146.5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>560.2 ± 129.8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>158.6 ± 41.1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>76.2 ± 9.8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>234.8 ± 43.7</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>108.6 ± 91.8</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>126.2 ± 124.4</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3285 ± 22</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7644 ± 573</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2712 ± 630</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3195 ± 0</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Door/image</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1094.8 ± 68.8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1169.3 ± 194.8</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>901.6 ± 169.6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1010.2 ± 95.9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>181.0 ± 25.8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>86.2 ± 14.2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>267.2 ± 37.2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>84.6 ± 34.9</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>182.6 ± 35.2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3292 ± 9</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>7495 ± 838</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2561 ± 917</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3195 ± 0</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Wipe/image</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1551.5 ± 142.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2011.8 ± 173.3</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1302.6 ± 105.7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1375.0 ± 141.4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>414.8 ± 20.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>294.4 ± 158.9</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>709.2 ± 141.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>176.5 ± 0.7</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>503.0 ± 33.9</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3247 ± 13</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>7551 ± 1632</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3657 ± 1715</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2392 ± 0</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="87" t="inlineStr">
+        <is>
+          <t>CAVEATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SINGLE SEED (seed 1). The P5 '±' is the round-to-round spread WITHIN one run — it is NOT a cross-seed error bar and must not be read as one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P1 is the FIRST round and is an UPPER bound on steady-state cost: the policy is at its weakest, so it fails most, which maximises the number of VLM/LLM calls and the screening rollouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REPORT BOTH NUMBERS. The raw Overhead x is close to 1 and UNDERSTATES the true cost of reasoning, because the shared from-scratch retrain + 100-episode eval dominate the denominator for BOTH arms. The reasoning-only add-on (DISEIL-specific s minus the baseline's gate s) is the honest marginal cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BUDGET ASYMMETRY (measured): DISEIL adds 1 demo/round, Diff-DAgger adds interventions_per_round=4. At BUDGET=5 Diff-DAgger hits final_demos and stops after only 2 rounds, so its 5-round P5 spread comes from a matched BUDGET=20 run (Nd=4 -&gt; exactly rounds 0..4). P1 is taken from the BUDGET=5 run for both arms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Backend: OpenRouter for all DISEIL runs. Token counts are NOT comparable across different backends (a local vLLM run would tokenise and bill differently).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Diff-DAgger's zeros in the token columns are structural, not unmeasured: the arm queries a diffusion-loss CDF quantile, never a foundation model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Every second in this sheet traces to a printed, timestamped event in a run that COMPLETED on this cluster. Diff-DAgger's history carries no per-round 'sec' key (baselines.py::_wrap_history), so its round wall-clock is derived from run.log timestamps ([train] -&gt; last [dagger ep]).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
